--- a/standalone/analysis/data/widgetsys.xlsx
+++ b/standalone/analysis/data/widgetsys.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/agamemnon/GitHub/quantrr/standalone/analysis/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6043671-6538-A64D-A7B2-349513BA53F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC17AA26-45FC-014C-8A9D-F144DB7F7516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="60" yWindow="500" windowWidth="28040" windowHeight="19900" activeTab="2" xr2:uid="{48D4EEF9-DFA2-7C44-84E9-995A687A38D6}"/>
+    <workbookView xWindow="60" yWindow="760" windowWidth="28040" windowHeight="17780" activeTab="2" xr2:uid="{48D4EEF9-DFA2-7C44-84E9-995A687A38D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Risks" sheetId="2" r:id="rId1"/>
@@ -617,13 +617,13 @@
         <v>11</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>9</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -679,13 +679,13 @@
         <v>1</v>
       </c>
       <c r="E5" s="3">
-        <v>2000</v>
+        <v>300000</v>
       </c>
       <c r="F5" s="3">
         <v>45000000</v>
       </c>
       <c r="G5" s="3">
-        <v>300000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -699,13 +699,13 @@
         <v>2</v>
       </c>
       <c r="E6" s="3">
-        <v>1400</v>
+        <v>200000</v>
       </c>
       <c r="F6" s="3">
         <v>34000000</v>
       </c>
       <c r="G6" s="3">
-        <v>200000</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -719,13 +719,13 @@
         <v>3</v>
       </c>
       <c r="E7" s="3">
-        <v>2100</v>
+        <v>500000</v>
       </c>
       <c r="F7" s="3">
         <v>54000000</v>
       </c>
       <c r="G7" s="3">
-        <v>500000</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -742,13 +742,13 @@
         <v>0.25</v>
       </c>
       <c r="E8" s="3">
-        <v>1900</v>
+        <v>275000</v>
       </c>
       <c r="F8" s="3">
         <v>44000000</v>
       </c>
       <c r="G8" s="3">
-        <v>275000</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -804,13 +804,13 @@
         <v>1</v>
       </c>
       <c r="E12" s="3">
-        <v>700</v>
+        <v>15000</v>
       </c>
       <c r="F12" s="3">
         <v>200000</v>
       </c>
       <c r="G12" s="3">
-        <v>15000</v>
+        <v>700</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
@@ -824,13 +824,13 @@
         <v>2</v>
       </c>
       <c r="E13" s="3">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F13" s="3">
         <v>150000</v>
       </c>
       <c r="G13" s="3">
-        <v>10000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
@@ -844,13 +844,13 @@
         <v>3</v>
       </c>
       <c r="E14" s="3">
-        <v>675</v>
+        <v>11000</v>
       </c>
       <c r="F14" s="3">
         <v>180000</v>
       </c>
       <c r="G14" s="3">
-        <v>11000</v>
+        <v>675</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
@@ -867,13 +867,13 @@
         <v>2</v>
       </c>
       <c r="E15" s="3">
-        <v>800</v>
+        <v>16000</v>
       </c>
       <c r="F15" s="3">
         <v>220000</v>
       </c>
       <c r="G15" s="3">
-        <v>16000</v>
+        <v>800</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
@@ -923,13 +923,13 @@
         <v>2</v>
       </c>
       <c r="E19" s="3">
-        <v>100000</v>
+        <v>1500000</v>
       </c>
       <c r="F19" s="3">
         <v>20000000</v>
       </c>
       <c r="G19" s="3">
-        <v>1500000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
@@ -946,13 +946,13 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
-        <v>150000</v>
+        <v>2000000</v>
       </c>
       <c r="F20" s="3">
         <v>30000000</v>
       </c>
       <c r="G20" s="3">
-        <v>2000000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
@@ -969,13 +969,13 @@
         <v>1</v>
       </c>
       <c r="E21" s="3">
-        <v>75000</v>
+        <v>1200000</v>
       </c>
       <c r="F21" s="3">
         <v>15000000</v>
       </c>
       <c r="G21" s="3">
-        <v>1200000</v>
+        <v>75000</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
@@ -992,13 +992,13 @@
         <v>2</v>
       </c>
       <c r="E22" s="3">
-        <v>75000</v>
+        <v>1000000</v>
       </c>
       <c r="F22" s="3">
         <v>15000000</v>
       </c>
       <c r="G22" s="3">
-        <v>1000000</v>
+        <v>75000</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
@@ -1054,13 +1054,13 @@
         <v>1</v>
       </c>
       <c r="E26" s="3">
-        <v>2000</v>
+        <v>300000</v>
       </c>
       <c r="F26" s="3">
         <v>45000000</v>
       </c>
       <c r="G26" s="3">
-        <v>300000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
@@ -1074,13 +1074,13 @@
         <v>2</v>
       </c>
       <c r="E27" s="3">
-        <v>1400</v>
+        <v>200000</v>
       </c>
       <c r="F27" s="3">
         <v>34000000</v>
       </c>
       <c r="G27" s="3">
-        <v>200000</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
@@ -1094,13 +1094,13 @@
         <v>3</v>
       </c>
       <c r="E28" s="3">
-        <v>2100</v>
+        <v>500000</v>
       </c>
       <c r="F28" s="3">
         <v>54000000</v>
       </c>
       <c r="G28" s="3">
-        <v>500000</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
@@ -1117,13 +1117,13 @@
         <v>0.1</v>
       </c>
       <c r="E29" s="3">
-        <v>1900</v>
+        <v>275000</v>
       </c>
       <c r="F29" s="3">
         <v>44000000</v>
       </c>
       <c r="G29" s="3">
-        <v>275000</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
@@ -1179,13 +1179,13 @@
         <v>1</v>
       </c>
       <c r="E33" s="3">
-        <v>700</v>
+        <v>10000</v>
       </c>
       <c r="F33" s="3">
         <v>150000</v>
       </c>
       <c r="G33" s="3">
-        <v>10000</v>
+        <v>700</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
@@ -1199,13 +1199,13 @@
         <v>2</v>
       </c>
       <c r="E34" s="3">
-        <v>500</v>
+        <v>7500</v>
       </c>
       <c r="F34" s="3">
         <v>125000</v>
       </c>
       <c r="G34" s="3">
-        <v>7500</v>
+        <v>500</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
@@ -1219,13 +1219,13 @@
         <v>3</v>
       </c>
       <c r="E35" s="3">
-        <v>675</v>
+        <v>10000</v>
       </c>
       <c r="F35" s="3">
         <v>160000</v>
       </c>
       <c r="G35" s="3">
-        <v>10000</v>
+        <v>675</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
@@ -1242,13 +1242,13 @@
         <v>1</v>
       </c>
       <c r="E36" s="3">
-        <v>800</v>
+        <v>11000</v>
       </c>
       <c r="F36" s="3">
         <v>155000</v>
       </c>
       <c r="G36" s="3">
-        <v>11000</v>
+        <v>800</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
@@ -1298,13 +1298,13 @@
         <v>0.2</v>
       </c>
       <c r="E40" s="3">
-        <v>100000</v>
+        <v>1500000</v>
       </c>
       <c r="F40" s="3">
         <v>20000000</v>
       </c>
       <c r="G40" s="3">
-        <v>1500000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
@@ -1321,13 +1321,13 @@
         <v>0.4</v>
       </c>
       <c r="E41" s="3">
-        <v>150000</v>
+        <v>2000000</v>
       </c>
       <c r="F41" s="3">
         <v>30000000</v>
       </c>
       <c r="G41" s="3">
-        <v>2000000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
@@ -1344,13 +1344,13 @@
         <v>0.25</v>
       </c>
       <c r="E42" s="3">
-        <v>75000</v>
+        <v>1200000</v>
       </c>
       <c r="F42" s="3">
         <v>15000000</v>
       </c>
       <c r="G42" s="3">
-        <v>1200000</v>
+        <v>75000</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
@@ -1367,13 +1367,13 @@
         <v>0.1</v>
       </c>
       <c r="E43" s="3">
-        <v>75000</v>
+        <v>1000000</v>
       </c>
       <c r="F43" s="3">
         <v>15000000</v>
       </c>
       <c r="G43" s="3">
-        <v>1000000</v>
+        <v>75000</v>
       </c>
     </row>
   </sheetData>
